--- a/Foundation of Data Analysis/Data-Exploration-Excel/Preparing-Data/VLOOKUP-Functions/Vlookup-function.xlsx
+++ b/Foundation of Data Analysis/Data-Exploration-Excel/Preparing-Data/VLOOKUP-Functions/Vlookup-function.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DS-ML-COURSE\Foundation of Data Analysis\Data-Exploration-Excel\Preparing-Data\VLOOKUP-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F30D0BB0-E9C9-444D-B5F3-C5749F29FC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB587CB9-3287-4461-8CFB-02466E23881E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5163A365-17CB-487D-8024-666E704B8C7C}"/>
   </bookViews>
@@ -24,10 +24,71 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -55,8 +116,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -371,9 +438,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D760E83-89A5-41AC-9CF9-968444391AA8}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:D13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <f>VLOOKUP(A13,A2:D7,4,0)</f>
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>